--- a/RFP.xlsx
+++ b/RFP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelshi/Desktop/Prod/RFP viewer/Source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C60A3C-5AAF-A240-BF9A-0B8BDB974D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72A2156A-B83A-324F-9C2A-24BF35FC03E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="74">
   <si>
     <t>Num</t>
   </si>
@@ -133,9 +133,6 @@
     <t>SOW/SLA/Impact/Risk review:</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 1 </t>
-  </si>
-  <si>
     <t>04/13/2025</t>
   </si>
   <si>
@@ -149,9 +146,6 @@
   </si>
   <si>
     <t>Procurement strategy/Vender list syncing</t>
-  </si>
-  <si>
-    <t>Phase 2</t>
   </si>
   <si>
     <t>04/14/2025</t>
@@ -648,7 +642,9 @@
   <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="49" customWidth="1"/>
+    <col min="2" max="2" width="42.1640625" customWidth="1"/>
+    <col min="3" max="3" width="61" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -694,7 +690,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -706,7 +702,7 @@
         <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -729,7 +725,7 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -741,7 +737,7 @@
         <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H3" t="s">
         <v>24</v>
@@ -764,7 +760,7 @@
         <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -799,7 +795,7 @@
         <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -834,7 +830,7 @@
         <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
         <v>36</v>
@@ -852,27 +848,27 @@
         <v>17</v>
       </c>
       <c r="I6" t="s">
+        <v>55</v>
+      </c>
+      <c r="J6" t="s">
         <v>37</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>38</v>
-      </c>
-      <c r="K6" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
         <v>40</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" t="s">
         <v>41</v>
-      </c>
-      <c r="C7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" t="s">
-        <v>42</v>
       </c>
       <c r="E7" t="s">
         <v>13</v>
@@ -887,27 +883,27 @@
         <v>17</v>
       </c>
       <c r="I7" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="J7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
         <v>13</v>
@@ -922,27 +918,27 @@
         <v>24</v>
       </c>
       <c r="I8" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="J8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E9" t="s">
         <v>13</v>
@@ -957,27 +953,27 @@
         <v>24</v>
       </c>
       <c r="I9" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="J9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E10" t="s">
         <v>13</v>
@@ -992,27 +988,27 @@
         <v>24</v>
       </c>
       <c r="I10" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="J10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
@@ -1027,27 +1023,27 @@
         <v>17</v>
       </c>
       <c r="I11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E12" t="s">
         <v>13</v>
@@ -1062,13 +1058,13 @@
         <v>17</v>
       </c>
       <c r="I12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1078,7 +1074,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:K1 A2:B12 D4:K12 D2:F2 H2:K2 D3:F3 H3:K3" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:K1 A2:B12 D4:K5 D2:F2 H2:K2 D3:F3 H3:K3 D11:K12 D10:H10 J10:K10 D9:H9 J9:K9 D8:H8 J8:K8 D7:H7 J7:K7 D6:H6 J6:K6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>